--- a/exports/WIPRO_full_report.xlsx
+++ b/exports/WIPRO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>1.89</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44573.55208333334</v>
+        <v>44574.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>330.2</v>
+        <v>311.9</v>
       </c>
       <c r="I2" t="n">
         <v>326.51</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.78</v>
+        <v>-6.28</v>
       </c>
       <c r="L2" t="n">
-        <v>1.89</v>
+        <v>6.94</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>4.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>5.92</v>
       </c>
       <c r="O2" t="n">
         <v>-1.95</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.82</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>275.95</v>
+        <v>281.1</v>
       </c>
       <c r="I3" t="n">
         <v>279.4888366870715</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>11.53</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L3" t="n">
         <v>2.02</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>8</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.38541666666</v>
+        <v>44606.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>263.25</v>
+        <v>259.2</v>
       </c>
       <c r="I4" t="n">
         <v>263.1123611304208</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.35</v>
+        <v>-7.79</v>
       </c>
       <c r="L4" t="n">
-        <v>8.16</v>
+        <v>8.18</v>
       </c>
       <c r="M4" t="n">
         <v>2.09</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>6.48</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44622.55208333334</v>
+        <v>44623.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>266.25</v>
+        <v>273.75</v>
       </c>
       <c r="I5" t="n">
         <v>273.3609534119188</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.72</v>
+        <v>-5.61</v>
       </c>
       <c r="L5" t="n">
-        <v>5.59</v>
+        <v>6.21</v>
       </c>
       <c r="M5" t="n">
         <v>1.88</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.7</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44657.55208333334</v>
+        <v>44658.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>283.6</v>
+        <v>279.1</v>
       </c>
       <c r="I6" t="n">
         <v>279.7441228235677</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="L6" t="n">
         <v>3.29</v>
@@ -783,7 +854,7 @@
         <v>1.84</v>
       </c>
       <c r="N6" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="O6" t="n">
         <v>2.38</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>4.24</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>223.5</v>
+        <v>228.35</v>
       </c>
       <c r="I7" t="n">
         <v>226.5558226577921</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K7" t="n">
-        <v>19.92</v>
+        <v>18.18</v>
       </c>
       <c r="L7" t="n">
         <v>1.38</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>5.84</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>220.4</v>
+        <v>215.15</v>
       </c>
       <c r="I8" t="n">
         <v>219.5476746256249</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.48</v>
+        <v>-5.78</v>
       </c>
       <c r="L8" t="n">
-        <v>4.49</v>
+        <v>6.79</v>
       </c>
       <c r="M8" t="n">
-        <v>1.76</v>
+        <v>2.43</v>
       </c>
       <c r="N8" t="n">
         <v>3.04</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>5.52</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44761.55208333334</v>
+        <v>44762.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>193.8</v>
+        <v>197.45</v>
       </c>
       <c r="I9" t="n">
         <v>196.6795244684802</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K9" t="n">
-        <v>9.92</v>
+        <v>8.23</v>
       </c>
       <c r="L9" t="n">
         <v>0.79</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.04</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>206.25</v>
+        <v>202.6</v>
       </c>
       <c r="I10" t="n">
         <v>204.8402243316567</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K10" t="n">
-        <v>4.46</v>
+        <v>2.61</v>
       </c>
       <c r="L10" t="n">
         <v>2.63</v>
@@ -1011,7 +1130,7 @@
         <v>0.71</v>
       </c>
       <c r="N10" t="n">
-        <v>2.35</v>
+        <v>2.64</v>
       </c>
       <c r="O10" t="n">
         <v>1.52</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>4.65</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44813.55208333334</v>
+        <v>44816.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>199.25</v>
+        <v>202.2</v>
       </c>
       <c r="I11" t="n">
         <v>200.0407727734825</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>1.65</v>
+        <v>0.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.65</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>3.94</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>198.1</v>
+        <v>193.8</v>
       </c>
       <c r="I12" t="n">
         <v>195.8785928288595</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.03</v>
+        <v>-4.15</v>
       </c>
       <c r="L12" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="M12" t="n">
         <v>3.27</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>2.93</v>
       </c>
       <c r="O12" t="n">
         <v>1.13</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>5.24</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>193.85</v>
+        <v>195.95</v>
       </c>
       <c r="I13" t="n">
         <v>194.921744465259</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.03</v>
+        <v>-1.11</v>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="M13" t="n">
         <v>1.46</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>4.3</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44846.55208333334</v>
+        <v>44847.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>195.3</v>
+        <v>181.3</v>
       </c>
       <c r="I14" t="n">
         <v>188.1206709228234</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.33</v>
+        <v>-7.48</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>7.76</v>
       </c>
       <c r="M14" t="n">
-        <v>1.75</v>
+        <v>5.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.41</v>
+        <v>7.12</v>
       </c>
       <c r="O14" t="n">
         <v>0.95</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44875.55208333334</v>
+        <v>44876.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>186.15</v>
+        <v>191</v>
       </c>
       <c r="I15" t="n">
         <v>188.8021383419823</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.68</v>
+        <v>-5.35</v>
       </c>
       <c r="L15" t="n">
-        <v>4.08</v>
+        <v>6.98</v>
       </c>
       <c r="M15" t="n">
-        <v>2.06</v>
+        <v>2.31</v>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>2.71</v>
       </c>
       <c r="O15" t="n">
         <v>-7.12</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>3.42</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>192.95</v>
+        <v>188.65</v>
       </c>
       <c r="I16" t="n">
         <v>190.962357229114</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K16" t="n">
-        <v>1.02</v>
+        <v>-1.23</v>
       </c>
       <c r="L16" t="n">
         <v>3.72</v>
@@ -1353,7 +1544,7 @@
         <v>0.61</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="O16" t="n">
         <v>2.71</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>4.91</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44924.55208333334</v>
+        <v>44925.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>186.9</v>
+        <v>188.6</v>
       </c>
       <c r="I17" t="n">
         <v>187.9724450361927</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>0.93</v>
+        <v>0.03</v>
       </c>
       <c r="L17" t="n">
         <v>2.86</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>3.41</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44931.55208333334</v>
+        <v>44932.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>185</v>
+        <v>182.7</v>
       </c>
       <c r="I18" t="n">
         <v>183.8909932819599</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.91</v>
+        <v>-3.13</v>
       </c>
       <c r="L18" t="n">
-        <v>2.76</v>
+        <v>3.26</v>
       </c>
       <c r="M18" t="n">
         <v>0.03</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>4.39</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44939.38541666666</v>
+        <v>44939.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>188.55</v>
+        <v>189</v>
       </c>
       <c r="I19" t="n">
         <v>188.9489618392419</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.2</v>
+        <v>-3.45</v>
       </c>
       <c r="L19" t="n">
         <v>4.08</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.2</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44978.55208333334</v>
+        <v>44979.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>192.4</v>
+        <v>189.65</v>
       </c>
       <c r="I20" t="n">
         <v>190.3548284167559</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>39</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K20" t="n">
-        <v>1.8</v>
+        <v>0.34</v>
       </c>
       <c r="L20" t="n">
         <v>1.38</v>
@@ -1581,7 +1820,7 @@
         <v>1.38</v>
       </c>
       <c r="N20" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
         <v>0.13</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>3.47</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45019.55208333334</v>
+        <v>45021.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>175.95</v>
+        <v>177.2</v>
       </c>
       <c r="I21" t="n">
         <v>176.3041970056839</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K21" t="n">
-        <v>7.22</v>
+        <v>6.56</v>
       </c>
       <c r="L21" t="n">
         <v>0.87</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>3.47</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45029.55208333334</v>
+        <v>45033.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>175.95</v>
+        <v>171.5</v>
       </c>
       <c r="I22" t="n">
         <v>173.0405740232523</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.71</v>
+        <v>-3.22</v>
       </c>
       <c r="L22" t="n">
-        <v>1.33</v>
+        <v>5.05</v>
       </c>
       <c r="M22" t="n">
-        <v>0.67</v>
+        <v>2.22</v>
       </c>
       <c r="N22" t="n">
-        <v>1.15</v>
+        <v>1.73</v>
       </c>
       <c r="O22" t="n">
         <v>0.45</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>3.34</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45037.55208333334</v>
+        <v>45040.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>175.85</v>
+        <v>180.35</v>
       </c>
       <c r="I23" t="n">
         <v>177.2270388879579</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.54</v>
+        <v>-5.16</v>
       </c>
       <c r="L23" t="n">
-        <v>2.74</v>
+        <v>5.31</v>
       </c>
       <c r="M23" t="n">
-        <v>0.43</v>
+        <v>1.91</v>
       </c>
       <c r="N23" t="n">
-        <v>1.42</v>
+        <v>2.73</v>
       </c>
       <c r="O23" t="n">
         <v>-1.73</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.78</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45089.38541666666</v>
+        <v>45089.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>190.1</v>
+        <v>189.05</v>
       </c>
       <c r="I24" t="n">
         <v>189.693594961197</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K24" t="n">
-        <v>5.41</v>
+        <v>4.82</v>
       </c>
       <c r="L24" t="n">
         <v>1.77</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>2.81</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45107.55208333334</v>
+        <v>45110.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>186</v>
+        <v>187.25</v>
       </c>
       <c r="I25" t="n">
         <v>186.5400823065323</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>1.61</v>
+        <v>0.95</v>
       </c>
       <c r="L25" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>0.82</v>
+        <v>1.21</v>
       </c>
       <c r="N25" t="n">
         <v>1.81</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>2.57</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45132.38541666666</v>
+        <v>45132.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>192.35</v>
+        <v>191.35</v>
       </c>
       <c r="I26" t="n">
         <v>191.4874423099677</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>2.72</v>
+        <v>2.19</v>
       </c>
       <c r="L26" t="n">
         <v>1.04</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>4.12</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45142.55208333334</v>
+        <v>45145.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>195.35</v>
+        <v>197.25</v>
       </c>
       <c r="I27" t="n">
         <v>196.6311012195908</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.09</v>
+        <v>-3.08</v>
       </c>
       <c r="L27" t="n">
-        <v>2.4</v>
+        <v>3.16</v>
       </c>
       <c r="M27" t="n">
         <v>0.76</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>3.89</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45190.55208333334</v>
+        <v>45191.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>204.6</v>
+        <v>201</v>
       </c>
       <c r="I28" t="n">
         <v>203.4426351199095</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K28" t="n">
-        <v>3.73</v>
+        <v>1.9</v>
       </c>
       <c r="L28" t="n">
         <v>1.52</v>
       </c>
       <c r="M28" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="N28" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="O28" t="n">
         <v>0.61</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>4.43</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>194.8</v>
+        <v>201.5</v>
       </c>
       <c r="I29" t="n">
         <v>199.3597285230518</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K29" t="n">
-        <v>3.08</v>
+        <v>-0.25</v>
       </c>
       <c r="L29" t="n">
         <v>1.49</v>
@@ -2094,7 +2441,7 @@
         <v>0.65</v>
       </c>
       <c r="N29" t="n">
-        <v>0.75</v>
+        <v>3.31</v>
       </c>
       <c r="O29" t="n">
         <v>-2.25</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>4.99</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45217.55208333334</v>
+        <v>45218.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>194.75</v>
+        <v>188.75</v>
       </c>
       <c r="I30" t="n">
         <v>194.203132322781</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.35</v>
+        <v>-6.33</v>
       </c>
       <c r="L30" t="n">
-        <v>3.45</v>
+        <v>7.47</v>
       </c>
       <c r="M30" t="n">
-        <v>1.15</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>1.36</v>
+        <v>3.06</v>
       </c>
       <c r="O30" t="n">
         <v>3.31</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>3.72</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45243.55208333334</v>
+        <v>45245.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>182.6</v>
+        <v>186.45</v>
       </c>
       <c r="I31" t="n">
         <v>185.4381079776452</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K31" t="n">
-        <v>3.26</v>
+        <v>1.22</v>
       </c>
       <c r="L31" t="n">
         <v>0.48</v>
@@ -2208,7 +2579,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>1.05</v>
+        <v>2.46</v>
       </c>
       <c r="O31" t="n">
         <v>-3.06</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>3.46</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45302.38541666666</v>
+        <v>45302.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>216</v>
+        <v>214.4</v>
       </c>
       <c r="I32" t="n">
         <v>215.2721108564326</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>57</v>
+        <v>57.16666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>15.85</v>
+        <v>14.99</v>
       </c>
       <c r="L32" t="n">
         <v>1.53</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>5.11</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45303.55208333334</v>
+        <v>45306.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>222.85</v>
+        <v>238.2</v>
       </c>
       <c r="I33" t="n">
         <v>225.3655216645699</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.94</v>
+        <v>-11.1</v>
       </c>
       <c r="L33" t="n">
-        <v>4.55</v>
+        <v>17.91</v>
       </c>
       <c r="M33" t="n">
-        <v>1.42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>3.94</v>
+        <v>6.13</v>
       </c>
       <c r="O33" t="n">
         <v>-1.61</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.02</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45356.55208333334</v>
+        <v>45357.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>245</v>
+        <v>241.25</v>
       </c>
       <c r="I34" t="n">
         <v>242.4141298373727</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K34" t="n">
-        <v>2.85</v>
+        <v>1.28</v>
       </c>
       <c r="L34" t="n">
         <v>6.3</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>5.41</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45404.55208333334</v>
+        <v>45405.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>220.8</v>
+        <v>221.7</v>
       </c>
       <c r="I35" t="n">
         <v>221.3967673476586</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K35" t="n">
-        <v>8.48</v>
+        <v>8.1</v>
       </c>
       <c r="L35" t="n">
         <v>3.5</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>4.95</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45440.55208333334</v>
+        <v>45441.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>217.45</v>
+        <v>215.95</v>
       </c>
       <c r="I36" t="n">
         <v>216.2125468003392</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.92</v>
+        <v>-2.59</v>
       </c>
       <c r="L36" t="n">
         <v>4.08</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>3.59</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45448.55208333334</v>
+        <v>45449.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>215.8</v>
+        <v>219.7</v>
       </c>
       <c r="I37" t="n">
         <v>217.2276053764522</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K37" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.74</v>
       </c>
       <c r="L37" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="M37" t="n">
         <v>2.55</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>6.07</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45492.55208333334</v>
+        <v>45495.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>266.2</v>
+        <v>240.6</v>
       </c>
       <c r="I38" t="n">
         <v>261.4936092493872</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K38" t="n">
-        <v>21.17</v>
+        <v>9.51</v>
       </c>
       <c r="L38" t="n">
         <v>1.55</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5</v>
+        <v>6.48</v>
       </c>
       <c r="N38" t="n">
-        <v>2.83</v>
+        <v>9.26</v>
       </c>
       <c r="O38" t="n">
         <v>2.13</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.51</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45518.55208333334</v>
+        <v>45520.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>236.9</v>
+        <v>245.25</v>
       </c>
       <c r="I39" t="n">
         <v>244.0614070938133</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K39" t="n">
-        <v>1.54</v>
+        <v>-1.93</v>
       </c>
       <c r="L39" t="n">
         <v>5.4</v>
@@ -2664,7 +3131,7 @@
         <v>1.77</v>
       </c>
       <c r="N39" t="n">
-        <v>3.36</v>
+        <v>4.12</v>
       </c>
       <c r="O39" t="n">
         <v>-9.26</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.87</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>249.2</v>
+        <v>247.65</v>
       </c>
       <c r="I40" t="n">
         <v>247.6733728877021</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>1.61</v>
+        <v>0.98</v>
       </c>
       <c r="L40" t="n">
         <v>2.96</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>4.05</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45547.55208333334</v>
+        <v>45548.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>252.6</v>
+        <v>261.95</v>
       </c>
       <c r="I41" t="n">
         <v>256.4364272858701</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>-2</v>
+        <v>-5.77</v>
       </c>
       <c r="L41" t="n">
-        <v>2.67</v>
+        <v>6.62</v>
       </c>
       <c r="M41" t="n">
-        <v>0.87</v>
+        <v>0.99</v>
       </c>
       <c r="N41" t="n">
-        <v>2.43</v>
+        <v>4.06</v>
       </c>
       <c r="O41" t="n">
         <v>-0.9399999999999999</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>6.27</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45572.55208333334</v>
+        <v>45573.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>253.6</v>
+        <v>249.75</v>
       </c>
       <c r="I42" t="n">
         <v>252.5357161730558</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.19</v>
+        <v>-4.66</v>
       </c>
       <c r="L42" t="n">
-        <v>4.03</v>
+        <v>5.06</v>
       </c>
       <c r="M42" t="n">
         <v>1.07</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.14</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45587.55208333334</v>
+        <v>45588.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>260.95</v>
+        <v>264.15</v>
       </c>
       <c r="I43" t="n">
         <v>263.9426361552914</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.48</v>
+        <v>-5.77</v>
       </c>
       <c r="L43" t="n">
         <v>7.53</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>6.63</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45597.75</v>
+        <v>45600.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>263.55</v>
+        <v>258</v>
       </c>
       <c r="I44" t="n">
         <v>258.2179554733614</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>9.364583333333334</v>
+        <v>12</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.23</v>
+        <v>-2.33</v>
       </c>
       <c r="L44" t="n">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="M44" t="n">
         <v>0.33</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>6.5</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45603.55208333334</v>
+        <v>45604.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>269.05</v>
+        <v>274</v>
       </c>
       <c r="I45" t="n">
         <v>272.3869662252813</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.28</v>
+        <v>-6.2</v>
       </c>
       <c r="L45" t="n">
-        <v>5.52</v>
+        <v>7.21</v>
       </c>
       <c r="M45" t="n">
         <v>0.62</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.66</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45656.55208333334</v>
+        <v>45657.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>291.2</v>
+        <v>287.6</v>
       </c>
       <c r="I46" t="n">
         <v>287.9258314733842</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K46" t="n">
-        <v>6.28</v>
+        <v>4.96</v>
       </c>
       <c r="L46" t="n">
         <v>5.75</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>3.95</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>269.25</v>
+        <v>286.45</v>
       </c>
       <c r="I47" t="n">
         <v>284.0252089895099</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>6.38</v>
+        <v>0.4</v>
       </c>
       <c r="L47" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="M47" t="n">
-        <v>1.13</v>
+        <v>6.7</v>
       </c>
       <c r="N47" t="n">
-        <v>2.2</v>
+        <v>6.69</v>
       </c>
       <c r="O47" t="n">
         <v>-0.88</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.39</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45702.55208333334</v>
+        <v>45705.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>300.9</v>
+        <v>295.15</v>
       </c>
       <c r="I48" t="n">
         <v>297.2225378068527</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K48" t="n">
-        <v>5.04</v>
+        <v>3.04</v>
       </c>
       <c r="L48" t="n">
         <v>0.93</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.28</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>235.65</v>
+        <v>249.35</v>
       </c>
       <c r="I49" t="n">
         <v>243.2085050178139</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>81.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K49" t="n">
-        <v>20.16</v>
+        <v>15.52</v>
       </c>
       <c r="L49" t="n">
         <v>4.54</v>
@@ -3234,7 +3821,7 @@
         <v>3.47</v>
       </c>
       <c r="N49" t="n">
-        <v>3.92</v>
+        <v>6.3</v>
       </c>
       <c r="O49" t="n">
         <v>-0.8100000000000001</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>7.72</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>258.45</v>
+        <v>252.4</v>
       </c>
       <c r="I50" t="n">
         <v>253.999237215454</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K50" t="n">
-        <v>3.65</v>
+        <v>1.22</v>
       </c>
       <c r="L50" t="n">
         <v>4.27</v>
       </c>
       <c r="M50" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="N50" t="n">
-        <v>2.02</v>
+        <v>2.65</v>
       </c>
       <c r="O50" t="n">
         <v>6.3</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>4.44</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45855.55208333334</v>
+        <v>45856.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>252.55</v>
+        <v>259.8</v>
       </c>
       <c r="I51" t="n">
         <v>257.7316983232354</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.06</v>
+        <v>-2.93</v>
       </c>
       <c r="L51" t="n">
-        <v>2.1</v>
+        <v>5.01</v>
       </c>
       <c r="M51" t="n">
-        <v>0.31</v>
+        <v>3.68</v>
       </c>
       <c r="N51" t="n">
-        <v>2.15</v>
+        <v>2.91</v>
       </c>
       <c r="O51" t="n">
         <v>-2.65</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>4.63</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>253.3</v>
+        <v>244.2</v>
       </c>
       <c r="I52" t="n">
         <v>247.7710063827614</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.5</v>
+        <v>-6</v>
       </c>
       <c r="L52" t="n">
-        <v>3.93</v>
+        <v>6.2</v>
       </c>
       <c r="M52" t="n">
-        <v>0.16</v>
+        <v>2.25</v>
       </c>
       <c r="N52" t="n">
-        <v>2.1</v>
+        <v>3.71</v>
       </c>
       <c r="O52" t="n">
         <v>2.91</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>5.83</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>241.25</v>
+        <v>245.65</v>
       </c>
       <c r="I53" t="n">
         <v>243.5686638912831</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K53" t="n">
-        <v>1.21</v>
+        <v>-0.59</v>
       </c>
       <c r="L53" t="n">
         <v>1.39</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>5.28</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45904.55208333334</v>
+        <v>45905.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>239.25</v>
+        <v>237.45</v>
       </c>
       <c r="I54" t="n">
         <v>237.4989417135758</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.61</v>
+        <v>-3.34</v>
       </c>
       <c r="L54" t="n">
-        <v>2.99</v>
+        <v>4.25</v>
       </c>
       <c r="M54" t="n">
         <v>0.87</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>4.16</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>242.95</v>
+        <v>250</v>
       </c>
       <c r="I55" t="n">
         <v>245.0569757165877</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.32</v>
+        <v>-5.29</v>
       </c>
       <c r="L55" t="n">
-        <v>2.57</v>
+        <v>5.58</v>
       </c>
       <c r="M55" t="n">
         <v>0.91</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.46</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>243.1</v>
+        <v>239</v>
       </c>
       <c r="I56" t="n">
         <v>242.6366778430649</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.76</v>
+        <v>-4.4</v>
       </c>
       <c r="L56" t="n">
-        <v>3.6</v>
+        <v>4.64</v>
       </c>
       <c r="M56" t="n">
         <v>3.02</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.62</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45938.55208333334</v>
+        <v>45939.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>237.85</v>
+        <v>239.7</v>
       </c>
       <c r="I57" t="n">
         <v>239.5972227809051</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K57" t="n">
-        <v>0.48</v>
+        <v>-0.29</v>
       </c>
       <c r="L57" t="n">
         <v>1.61</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>3.72</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45946.55208333334</v>
+        <v>45947.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>247.3</v>
+        <v>233.9</v>
       </c>
       <c r="I58" t="n">
         <v>238.347009817458</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K58" t="n">
-        <v>3.17</v>
+        <v>-2.42</v>
       </c>
       <c r="L58" t="n">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="M58" t="n">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="N58" t="n">
-        <v>1.52</v>
+        <v>5.14</v>
       </c>
       <c r="O58" t="n">
         <v>0.99</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.09</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>235.6</v>
+        <v>239.65</v>
       </c>
       <c r="I59" t="n">
         <v>237.0229164861669</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.73</v>
+        <v>-2.46</v>
       </c>
       <c r="L59" t="n">
         <v>4.19</v>
@@ -3804,7 +4511,7 @@
         <v>1.51</v>
       </c>
       <c r="N59" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="O59" t="n">
         <v>-5.14</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>3.66</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46021.55208333334</v>
+        <v>46022.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>257.45</v>
+        <v>255.4</v>
       </c>
       <c r="I60" t="n">
         <v>256.6428212828567</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K60" t="n">
-        <v>7.43</v>
+        <v>6.57</v>
       </c>
       <c r="L60" t="n">
         <v>2.25</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>2.95</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>260.55</v>
+        <v>263.65</v>
       </c>
       <c r="I61" t="n">
         <v>262.9369088766322</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.02</v>
+        <v>-3.23</v>
       </c>
       <c r="L61" t="n">
-        <v>2.31</v>
+        <v>3.97</v>
       </c>
       <c r="M61" t="n">
         <v>0.27</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>3.57</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46035.55208333334</v>
+        <v>46036.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>257.75</v>
+        <v>254.4</v>
       </c>
       <c r="I62" t="n">
         <v>254.6641474274375</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.24</v>
+        <v>-3.51</v>
       </c>
       <c r="L62" t="n">
         <v>4.21</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>4.49</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46114.55208333334</v>
+        <v>46118.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>194.8</v>
+        <v>197.9</v>
       </c>
       <c r="I63" t="n">
         <v>197.5167782979974</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>78.16666666666667</v>
+        <v>82</v>
       </c>
       <c r="K63" t="n">
-        <v>23.43</v>
+        <v>22.21</v>
       </c>
       <c r="L63" t="n">
         <v>3.38</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.28</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>202.87</v>
+        <v>198.38</v>
       </c>
       <c r="I64" t="n">
         <v>199.5138312194789</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K64" t="n">
-        <v>2.51</v>
+        <v>0.24</v>
       </c>
       <c r="L64" t="n">
         <v>0.9</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.38</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46160.55208333334</v>
+        <v>46161.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>192.49</v>
+        <v>195.38</v>
       </c>
       <c r="I65" t="n">
         <v>194.9046276264903</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K65" t="n">
-        <v>2.97</v>
+        <v>1.51</v>
       </c>
       <c r="L65" t="n">
         <v>3.68</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>4.19</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46177.55208333334</v>
+        <v>46178.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>204</v>
+        <v>195.37</v>
       </c>
       <c r="I66" t="n">
         <v>200.2459878361297</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K66" t="n">
-        <v>4.41</v>
+        <v>-0.01</v>
       </c>
       <c r="L66" t="n">
-        <v>1.53</v>
+        <v>3.7</v>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>6.12</v>
       </c>
       <c r="N66" t="n">
         <v>2.95</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.29</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46213.55208333334</v>
+        <v>46216.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>175.52</v>
+        <v>179.55</v>
       </c>
       <c r="I67" t="n">
         <v>178.4881786336597</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K67" t="n">
-        <v>10.16</v>
+        <v>8.1</v>
       </c>
       <c r="L67" t="n">
         <v>1.86</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.03</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46251.55208333334</v>
+        <v>46252.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>182.1</v>
+        <v>179.15</v>
       </c>
       <c r="I68" t="n">
         <v>180.2229171835355</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K68" t="n">
-        <v>1.42</v>
+        <v>-0.22</v>
       </c>
       <c r="L68" t="n">
         <v>3.76</v>
@@ -4317,7 +5132,7 @@
         <v>2.33</v>
       </c>
       <c r="N68" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="O68" t="n">
         <v>1.65</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>4.12</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46307.55208333334</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>161.4</v>
+        <v>167.54</v>
       </c>
       <c r="I69" t="n">
         <v>164.8365852584895</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K69" t="n">
-        <v>9.91</v>
+        <v>6.48</v>
       </c>
       <c r="L69" t="n">
         <v>2.66</v>
@@ -4374,7 +5201,7 @@
         <v>2.92</v>
       </c>
       <c r="N69" t="n">
-        <v>2.24</v>
+        <v>4.46</v>
       </c>
       <c r="O69" t="n">
         <v>-1.88</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4434,6 +5273,12 @@
       <c r="Q70" t="n">
         <v>20</v>
       </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6536,7 +7381,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.1</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="6">
@@ -6546,7 +7391,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.7</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="7">
@@ -6556,7 +7401,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>81.2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -6566,7 +7411,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6576,7 +7421,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.2</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="10">
@@ -6586,7 +7431,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50.2</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="11">
@@ -6626,7 +7471,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.57</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="15">
@@ -6636,7 +7481,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.87</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="16">
@@ -6646,7 +7491,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.26</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="17">
@@ -6656,7 +7501,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23.43</v>
+        <v>22.21</v>
       </c>
     </row>
     <row r="18">
@@ -6666,7 +7511,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.4</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="19">
@@ -6676,7 +7521,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.88</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="20">
@@ -6686,7 +7531,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.64</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="21">
@@ -6696,7 +7541,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.16</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="22">
@@ -6706,7 +7551,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -6716,7 +7561,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6726,7 +7571,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="25">
@@ -6736,7 +7581,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.89</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -6746,7 +7591,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.35</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="27">
@@ -6756,7 +7601,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.2</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="28">
@@ -6766,7 +7611,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
